--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="iavyuqSGVBouZT/wo81LSAtJV3csI1UJGFrGOFZspIM="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="O/MmoBhCHmbCt2vqMpOSZ5ejoPGlLlYw0GKey/gO7nE="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="22">
   <si>
     <t>고유ID</t>
   </si>
@@ -63,9 +63,6 @@
     <t>AttackDelay</t>
   </si>
   <si>
-    <t>AttackDamage</t>
-  </si>
-  <si>
     <t>PrefabAddress</t>
   </si>
   <si>
@@ -85,12 +82,6 @@
   </si>
   <si>
     <t>Police_Throw</t>
-  </si>
-  <si>
-    <t>Enemy_04</t>
-  </si>
-  <si>
-    <t>Police_Dog</t>
   </si>
 </sst>
 </file>
@@ -356,9 +347,8 @@
     <col customWidth="1" min="8" max="8" width="33.43"/>
     <col customWidth="1" min="9" max="9" width="31.29"/>
     <col customWidth="1" min="10" max="11" width="29.86"/>
-    <col customWidth="1" min="12" max="12" width="31.43"/>
-    <col customWidth="1" min="13" max="13" width="40.14"/>
-    <col customWidth="1" min="14" max="27" width="8.71"/>
+    <col customWidth="1" min="12" max="12" width="40.14"/>
+    <col customWidth="1" min="13" max="26" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.25" customHeight="1">
@@ -401,9 +391,6 @@
         <v>3</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -444,16 +431,13 @@
       <c r="L3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M3" s="1" t="s">
-        <v>16</v>
-      </c>
     </row>
     <row r="4" ht="17.25" customHeight="1">
       <c r="A4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="C4" s="1">
         <v>5.0</v>
@@ -482,19 +466,16 @@
       <c r="K4" s="1">
         <v>0.0</v>
       </c>
-      <c r="L4" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>18</v>
+      <c r="L4" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
       <c r="A5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="C5" s="1">
         <v>8.0</v>
@@ -523,19 +504,16 @@
       <c r="K5" s="1">
         <v>1.5</v>
       </c>
-      <c r="L5" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>20</v>
+      <c r="L5" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
       <c r="A6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="C6" s="1">
         <v>10.0</v>
@@ -564,54 +542,11 @@
       <c r="K6" s="1">
         <v>1.0</v>
       </c>
-      <c r="L6" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>22</v>
+      <c r="L6" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="7" ht="17.25" customHeight="1">
-      <c r="A7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="1">
-        <v>20.0</v>
-      </c>
-      <c r="D7" s="1">
-        <v>200.0</v>
-      </c>
-      <c r="E7" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="F7" s="1">
-        <v>30.0</v>
-      </c>
-      <c r="G7" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="H7" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="I7" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="J7" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="K7" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="L7" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
+    <row r="7" ht="17.25" customHeight="1"/>
     <row r="8" ht="17.25" customHeight="1"/>
     <row r="9" ht="17.25" customHeight="1"/>
     <row r="10" ht="17.25" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -448,8 +448,8 @@
       <c r="E4" s="1">
         <v>0.8</v>
       </c>
-      <c r="F4" s="1">
-        <v>10.0</v>
+      <c r="F4" s="2">
+        <v>15.0</v>
       </c>
       <c r="G4" s="1">
         <v>3.0</v>
@@ -486,8 +486,8 @@
       <c r="E5" s="1">
         <v>1.2</v>
       </c>
-      <c r="F5" s="1">
-        <v>12.0</v>
+      <c r="F5" s="2">
+        <v>18.0</v>
       </c>
       <c r="G5" s="1">
         <v>3.0</v>
@@ -524,8 +524,8 @@
       <c r="E6" s="1">
         <v>0.7</v>
       </c>
-      <c r="F6" s="1">
-        <v>12.0</v>
+      <c r="F6" s="2">
+        <v>18.0</v>
       </c>
       <c r="G6" s="1">
         <v>2.0</v>
@@ -546,7 +546,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" ht="17.25" customHeight="1"/>
+    <row r="7" ht="17.25" customHeight="1">
+      <c r="F7" s="2"/>
+    </row>
     <row r="8" ht="17.25" customHeight="1"/>
     <row r="9" ht="17.25" customHeight="1"/>
     <row r="10" ht="17.25" customHeight="1"/>
